--- a/student_timetable_data.xlsx
+++ b/student_timetable_data.xlsx
@@ -30,7 +30,7 @@
     <t xml:space="preserve">Hours</t>
   </si>
   <si>
-    <t xml:space="preserve">Livin</t>
+    <t xml:space="preserve">Livin_U</t>
   </si>
   <si>
     <t xml:space="preserve">Mercy</t>
